--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260813.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260813.xlsx
@@ -821,17 +821,17 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>1,221,617</t>
+          <t>188,515</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -843,17 +843,17 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>188,515</t>
+          <t>1,221,617</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>1,381,000</t>
+          <t>884,349</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>884,349</t>
+          <t>1,381,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>202608WTEQ6F</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>電子指數期貨</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>596,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>202608WTEQ6F</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>電子指數期貨</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>596,000</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>3,592,981</t>
+          <t>2,680,703</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>2,680,703</t>
+          <t>3,592,981</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>202608WVHFQ6F</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>96,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>202608WVHFQ6F</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>402,000</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>96,000</t>
+          <t>402,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>235,000</t>
+          <t>5,119,956</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>5,119,956</t>
+          <t>235,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>1,610,400</t>
+          <t>300,000</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>300,000</t>
+          <t>1,610,400</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1943,17 +1943,17 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>1,035,121</t>
+          <t>119,000</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>119,000</t>
+          <t>1,035,121</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>176,000</t>
+          <t>184,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>184,000</t>
+          <t>176,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2097,17 +2097,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>262,000</t>
+          <t>162,000</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -2119,17 +2119,17 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>162,000</t>
+          <t>702,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>702,000</t>
+          <t>262,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
